--- a/tests/TTA_manual_expected_results.xlsx
+++ b/tests/TTA_manual_expected_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sbramer\HOME\PROJECTS\Hanford\CodeReview\TobitTrendAnalysis\Tobit2.0\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD70909-21EB-4310-B904-D819FE74BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F82469A-CDC2-45D1-9619-C5B12C552E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{71A84E4C-F866-483E-B1D8-B8BE7DFA33A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{71A84E4C-F866-483E-B1D8-B8BE7DFA33A5}"/>
   </bookViews>
   <sheets>
     <sheet name="01_event_only" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Stefan Bramer:</t>
         </r>
@@ -65,7 +65,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 compare with </t>
@@ -152,7 +152,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Stefan Bramer:</t>
         </r>
@@ -161,7 +161,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 River Stage</t>
@@ -176,7 +176,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Stefan Bramer:</t>
         </r>
@@ -185,7 +185,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 compare with </t>
@@ -315,7 +315,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Stefan Bramer:</t>
         </r>
@@ -324,7 +324,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 River Stage</t>
@@ -339,7 +339,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Stefan Bramer:</t>
         </r>
@@ -348,7 +348,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 compare with </t>
@@ -465,7 +465,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -487,7 +487,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="13">
   <si>
     <t>EVENT</t>
   </si>
@@ -524,6 +524,9 @@
   <si>
     <t>Tobit check not possible in Excel, external tool needed?</t>
   </si>
+  <si>
+    <t>Manual expected results for Borehole 199-H3-9 - INTERP + EVENT</t>
+  </si>
 </sst>
 </file>
 
@@ -532,7 +535,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,23 +547,10 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
@@ -634,28 +624,28 @@
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -991,22 +981,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{475BC072-179B-442E-B2B5-C659274754BE}">
   <dimension ref="A1:J57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="8" customWidth="1"/>
-    <col min="2" max="5" width="11.140625" style="6" customWidth="1"/>
-    <col min="6" max="8" width="9.140625" style="6"/>
-    <col min="9" max="9" width="12.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="11.1328125" style="8" customWidth="1"/>
+    <col min="2" max="5" width="11.1328125" style="6" customWidth="1"/>
+    <col min="6" max="8" width="9.1328125" style="6"/>
+    <col min="9" max="9" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1032,7 +1022,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>39833</v>
       </c>
@@ -1062,7 +1052,7 @@
         <v>10.115804477424177</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
         <v>39856</v>
       </c>
@@ -1092,7 +1082,7 @@
         <v>17.980625626721725</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
         <v>39895</v>
       </c>
@@ -1111,7 +1101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="8">
         <v>39916</v>
       </c>
@@ -1131,7 +1121,7 @@
       </c>
       <c r="H6" s="9"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="8">
         <v>39979</v>
       </c>
@@ -1150,7 +1140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
         <v>40162</v>
       </c>
@@ -1169,7 +1159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="8">
         <v>40248</v>
       </c>
@@ -1188,7 +1178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="8">
         <v>40274</v>
       </c>
@@ -1207,7 +1197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="8">
         <v>40380</v>
       </c>
@@ -1226,7 +1216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="8">
         <v>40429</v>
       </c>
@@ -1245,7 +1235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="8">
         <v>40573</v>
       </c>
@@ -1264,7 +1254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="8">
         <v>40665</v>
       </c>
@@ -1283,7 +1273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="8">
         <v>40779</v>
       </c>
@@ -1302,7 +1292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="8">
         <v>40829</v>
       </c>
@@ -1321,7 +1311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="8">
         <v>40946</v>
       </c>
@@ -1340,7 +1330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="8">
         <v>41058</v>
       </c>
@@ -1359,7 +1349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="8">
         <v>41079</v>
       </c>
@@ -1378,7 +1368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="8">
         <v>41233</v>
       </c>
@@ -1397,7 +1387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="8">
         <v>41318</v>
       </c>
@@ -1416,7 +1406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="8">
         <v>41415</v>
       </c>
@@ -1435,7 +1425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="8">
         <v>41530</v>
       </c>
@@ -1454,7 +1444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="8">
         <v>41628</v>
       </c>
@@ -1473,7 +1463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="8">
         <v>41722</v>
       </c>
@@ -1492,7 +1482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="8">
         <v>41810</v>
       </c>
@@ -1511,7 +1501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="8">
         <v>41887</v>
       </c>
@@ -1530,7 +1520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="8">
         <v>41992</v>
       </c>
@@ -1549,7 +1539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="8">
         <v>42062</v>
       </c>
@@ -1568,7 +1558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="8">
         <v>42153</v>
       </c>
@@ -1587,7 +1577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="8">
         <v>42242</v>
       </c>
@@ -1606,7 +1596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="8">
         <v>42444</v>
       </c>
@@ -1625,7 +1615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="8">
         <v>42540</v>
       </c>
@@ -1644,7 +1634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" s="8">
         <v>39939</v>
       </c>
@@ -1663,7 +1653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="8">
         <v>40015</v>
       </c>
@@ -1682,7 +1672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="8">
         <v>40036</v>
       </c>
@@ -1701,7 +1691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="8">
         <v>40070</v>
       </c>
@@ -1720,7 +1710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="8">
         <v>40094</v>
       </c>
@@ -1739,7 +1729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="8">
         <v>40126</v>
       </c>
@@ -1758,7 +1748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="8">
         <v>40193</v>
       </c>
@@ -1777,7 +1767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="8">
         <v>40220</v>
       </c>
@@ -1796,7 +1786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="8">
         <v>40314</v>
       </c>
@@ -1815,7 +1805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="8">
         <v>40352</v>
       </c>
@@ -1834,7 +1824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="8">
         <v>40407</v>
       </c>
@@ -1853,7 +1843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="8">
         <v>40638</v>
       </c>
@@ -1872,7 +1862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="8">
         <v>40687</v>
       </c>
@@ -1891,7 +1881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="8">
         <v>40714</v>
       </c>
@@ -1910,7 +1900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="8">
         <v>42356</v>
       </c>
@@ -1929,7 +1919,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="8">
         <v>42712</v>
       </c>
@@ -1948,7 +1938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="8">
         <v>43077</v>
       </c>
@@ -1967,7 +1957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="8">
         <v>43448</v>
       </c>
@@ -1986,7 +1976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="8">
         <v>43802</v>
       </c>
@@ -2005,7 +1995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="8">
         <v>44172</v>
       </c>
@@ -2024,7 +2014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="8">
         <v>44515</v>
       </c>
@@ -2043,7 +2033,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="8">
         <v>44865</v>
       </c>
@@ -2062,7 +2052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="8">
         <v>45155</v>
       </c>
@@ -2081,7 +2071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="8">
         <v>45344</v>
       </c>
@@ -2109,22 +2099,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D63709-B220-4FD3-9373-D06705FD91B9}">
   <dimension ref="A1:M183"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="8" customWidth="1"/>
-    <col min="2" max="6" width="11.140625" style="6" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="6"/>
-    <col min="10" max="12" width="12.42578125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" style="8" customWidth="1"/>
+    <col min="2" max="6" width="11.1328125" style="6" customWidth="1"/>
+    <col min="7" max="9" width="9.1328125" style="6"/>
+    <col min="10" max="12" width="12.3984375" style="6" customWidth="1"/>
     <col min="13" max="13" width="37" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="6"/>
+    <col min="14" max="16384" width="9.1328125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2156,7 +2146,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>39512</v>
       </c>
@@ -2193,7 +2183,7 @@
         <v>3.5959451854528623</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
         <v>39583</v>
       </c>
@@ -2230,7 +2220,7 @@
         <v>49.462755012965317</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
         <v>39684</v>
       </c>
@@ -2270,7 +2260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" s="8">
         <v>39771</v>
       </c>
@@ -2293,7 +2283,7 @@
       </c>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="8">
         <v>39869</v>
       </c>
@@ -2314,8 +2304,11 @@
       <c r="F7" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
         <v>39940</v>
       </c>
@@ -2337,9 +2330,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="10"/>
-      <c r="K8" s="11"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" s="8">
         <v>40035</v>
       </c>
@@ -2363,7 +2357,7 @@
       <c r="J9" s="10"/>
       <c r="K9" s="11"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="8">
         <v>40094</v>
       </c>
@@ -2385,7 +2379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" s="8">
         <v>40261</v>
       </c>
@@ -2407,7 +2401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" s="8">
         <v>40332</v>
       </c>
@@ -2429,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" s="8">
         <v>40546</v>
       </c>
@@ -2451,7 +2445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" s="8">
         <v>40589</v>
       </c>
@@ -2473,7 +2467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" s="8">
         <v>40616</v>
       </c>
@@ -2495,7 +2489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="8">
         <v>40673</v>
       </c>
@@ -2517,7 +2511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="8">
         <v>40696</v>
       </c>
@@ -2539,7 +2533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="8">
         <v>40729</v>
       </c>
@@ -2561,7 +2555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="8">
         <v>40757</v>
       </c>
@@ -2583,7 +2577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="8">
         <v>40787</v>
       </c>
@@ -2605,7 +2599,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="8">
         <v>40821</v>
       </c>
@@ -2627,7 +2621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="8">
         <v>40849</v>
       </c>
@@ -2649,7 +2643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="8">
         <v>40884</v>
       </c>
@@ -2671,7 +2665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="8">
         <v>40952</v>
       </c>
@@ -2693,7 +2687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="8">
         <v>40976</v>
       </c>
@@ -2715,7 +2709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="8">
         <v>41002</v>
       </c>
@@ -2737,7 +2731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="8">
         <v>41028</v>
       </c>
@@ -2759,7 +2753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="8">
         <v>41065</v>
       </c>
@@ -2781,7 +2775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="8">
         <v>41101</v>
       </c>
@@ -2803,7 +2797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="8">
         <v>41112</v>
       </c>
@@ -2825,7 +2819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="8">
         <v>41122</v>
       </c>
@@ -2847,7 +2841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="8">
         <v>41157</v>
       </c>
@@ -2869,7 +2863,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="8">
         <v>41183</v>
       </c>
@@ -2891,7 +2885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" s="8">
         <v>41210</v>
       </c>
@@ -2913,7 +2907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" s="8">
         <v>41218</v>
       </c>
@@ -2935,7 +2929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" s="8">
         <v>41246</v>
       </c>
@@ -2957,7 +2951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" s="8">
         <v>41281</v>
       </c>
@@ -2979,7 +2973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" s="8">
         <v>41309</v>
       </c>
@@ -3001,7 +2995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="8">
         <v>41345</v>
       </c>
@@ -3023,7 +3017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" s="8">
         <v>41366</v>
       </c>
@@ -3045,7 +3039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" s="8">
         <v>41400</v>
       </c>
@@ -3067,7 +3061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" s="8">
         <v>41407</v>
       </c>
@@ -3089,7 +3083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" s="8">
         <v>41429</v>
       </c>
@@ -3111,7 +3105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" s="8">
         <v>41457</v>
       </c>
@@ -3133,7 +3127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" s="8">
         <v>41492</v>
       </c>
@@ -3155,7 +3149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" s="8">
         <v>41494</v>
       </c>
@@ -3177,7 +3171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" s="8">
         <v>41521</v>
       </c>
@@ -3199,7 +3193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="8">
         <v>41562</v>
       </c>
@@ -3221,7 +3215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" s="8">
         <v>41585</v>
       </c>
@@ -3243,7 +3237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="8">
         <v>41624</v>
       </c>
@@ -3265,7 +3259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="8">
         <v>41641</v>
       </c>
@@ -3287,7 +3281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" s="8">
         <v>41690</v>
       </c>
@@ -3309,7 +3303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" s="8">
         <v>41702</v>
       </c>
@@ -3331,7 +3325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" s="8">
         <v>41730</v>
       </c>
@@ -3353,7 +3347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" s="8">
         <v>41765</v>
       </c>
@@ -3375,7 +3369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" s="8">
         <v>41802</v>
       </c>
@@ -3397,7 +3391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" s="8">
         <v>41822</v>
       </c>
@@ -3419,7 +3413,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" s="8">
         <v>41857</v>
       </c>
@@ -3441,7 +3435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" s="8">
         <v>41892</v>
       </c>
@@ -3463,7 +3457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" s="8">
         <v>41914</v>
       </c>
@@ -3485,7 +3479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" s="8">
         <v>41963</v>
       </c>
@@ -3507,7 +3501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" s="8">
         <v>41975</v>
       </c>
@@ -3529,7 +3523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" s="8">
         <v>42012</v>
       </c>
@@ -3551,7 +3545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" s="8">
         <v>42038</v>
       </c>
@@ -3573,7 +3567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="8">
         <v>42073</v>
       </c>
@@ -3595,7 +3589,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" s="8">
         <v>42103</v>
       </c>
@@ -3617,7 +3611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" s="8">
         <v>42137</v>
       </c>
@@ -3639,7 +3633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" s="8">
         <v>42164</v>
       </c>
@@ -3661,7 +3655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" s="8">
         <v>42213</v>
       </c>
@@ -3683,7 +3677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" s="8">
         <v>42219</v>
       </c>
@@ -3705,7 +3699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" s="8">
         <v>42268</v>
       </c>
@@ -3727,7 +3721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" s="8">
         <v>42297</v>
       </c>
@@ -3749,7 +3743,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A73" s="8">
         <v>42326</v>
       </c>
@@ -3771,7 +3765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A74" s="8">
         <v>42359</v>
       </c>
@@ -3793,7 +3787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A75" s="8">
         <v>42373</v>
       </c>
@@ -3815,7 +3809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" s="8">
         <v>42403</v>
       </c>
@@ -3837,7 +3831,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" s="8">
         <v>42436</v>
       </c>
@@ -3859,7 +3853,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" s="8">
         <v>42478</v>
       </c>
@@ -3881,7 +3875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" s="8">
         <v>42534</v>
       </c>
@@ -3903,7 +3897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" s="8">
         <v>42556</v>
       </c>
@@ -3925,7 +3919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81" s="8">
         <v>42585</v>
       </c>
@@ -3947,7 +3941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" s="8">
         <v>42599</v>
       </c>
@@ -3969,7 +3963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83" s="8">
         <v>42684</v>
       </c>
@@ -3991,7 +3985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" s="8">
         <v>42723</v>
       </c>
@@ -4013,7 +4007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85" s="8">
         <v>42752</v>
       </c>
@@ -4035,7 +4029,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86" s="8">
         <v>42795</v>
       </c>
@@ -4057,7 +4051,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87" s="8">
         <v>42822</v>
       </c>
@@ -4079,7 +4073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88" s="8">
         <v>42850</v>
       </c>
@@ -4101,7 +4095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89" s="8">
         <v>42856</v>
       </c>
@@ -4123,7 +4117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A90" s="8">
         <v>42892</v>
       </c>
@@ -4145,7 +4139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91" s="8">
         <v>42905</v>
       </c>
@@ -4167,7 +4161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92" s="8">
         <v>42929</v>
       </c>
@@ -4189,7 +4183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93" s="8">
         <v>42954</v>
       </c>
@@ -4211,7 +4205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94" s="8">
         <v>42962</v>
       </c>
@@ -4233,7 +4227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95" s="8">
         <v>42989</v>
       </c>
@@ -4255,7 +4249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96" s="8">
         <v>43026</v>
       </c>
@@ -4277,7 +4271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" s="8">
         <v>43047</v>
       </c>
@@ -4299,7 +4293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A98" s="8">
         <v>43054</v>
       </c>
@@ -4321,7 +4315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99" s="8">
         <v>43075</v>
       </c>
@@ -4343,7 +4337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100" s="8">
         <v>43151</v>
       </c>
@@ -4365,7 +4359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101" s="8">
         <v>43173</v>
       </c>
@@ -4387,7 +4381,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" s="8">
         <v>43200</v>
       </c>
@@ -4409,7 +4403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A103" s="8">
         <v>43234</v>
       </c>
@@ -4431,7 +4425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" s="8">
         <v>43271</v>
       </c>
@@ -4453,7 +4447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" s="8">
         <v>43290</v>
       </c>
@@ -4475,7 +4469,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" s="8">
         <v>43334</v>
       </c>
@@ -4497,7 +4491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" s="8">
         <v>43368</v>
       </c>
@@ -4519,7 +4513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A108" s="8">
         <v>43432</v>
       </c>
@@ -4541,7 +4535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A109" s="8">
         <v>43445</v>
       </c>
@@ -4563,7 +4557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A110" s="8">
         <v>43481</v>
       </c>
@@ -4585,7 +4579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111" s="8">
         <v>43502</v>
       </c>
@@ -4607,7 +4601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112" s="8">
         <v>43503</v>
       </c>
@@ -4629,7 +4623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A113" s="8">
         <v>43606</v>
       </c>
@@ -4651,7 +4645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114" s="8">
         <v>43608</v>
       </c>
@@ -4673,7 +4667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A115" s="8">
         <v>43633</v>
       </c>
@@ -4695,7 +4689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A116" s="8">
         <v>43657</v>
       </c>
@@ -4717,7 +4711,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A117" s="8">
         <v>43696</v>
       </c>
@@ -4739,7 +4733,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A118" s="8">
         <v>43717</v>
       </c>
@@ -4761,7 +4755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A119" s="8">
         <v>43768</v>
       </c>
@@ -4783,7 +4777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A120" s="8">
         <v>43789</v>
       </c>
@@ -4805,7 +4799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A121" s="8">
         <v>43790</v>
       </c>
@@ -4827,7 +4821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A122" s="8">
         <v>43815</v>
       </c>
@@ -4849,7 +4843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A123" s="8">
         <v>43837</v>
       </c>
@@ -4871,7 +4865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A124" s="8">
         <v>43872</v>
       </c>
@@ -4893,7 +4887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A125" s="8">
         <v>43886</v>
       </c>
@@ -4915,7 +4909,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A126" s="8">
         <v>44056</v>
       </c>
@@ -4937,7 +4931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A127" s="8">
         <v>44074</v>
       </c>
@@ -4959,7 +4953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A128" s="8">
         <v>44099</v>
       </c>
@@ -4981,7 +4975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A129" s="8">
         <v>44125</v>
       </c>
@@ -5003,7 +4997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A130" s="8">
         <v>44152</v>
       </c>
@@ -5025,7 +5019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A131" s="8">
         <v>44221</v>
       </c>
@@ -5047,7 +5041,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A132" s="8">
         <v>44236</v>
       </c>
@@ -5069,7 +5063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A133" s="8">
         <v>44245</v>
       </c>
@@ -5091,7 +5085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A134" s="8">
         <v>44273</v>
       </c>
@@ -5113,7 +5107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A135" s="8">
         <v>44333</v>
       </c>
@@ -5135,7 +5129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A136" s="8">
         <v>44336</v>
       </c>
@@ -5157,7 +5151,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A137" s="8">
         <v>44349</v>
       </c>
@@ -5179,7 +5173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A138" s="8">
         <v>44397</v>
       </c>
@@ -5201,7 +5195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A139" s="8">
         <v>44411</v>
       </c>
@@ -5223,7 +5217,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A140" s="8">
         <v>44434</v>
       </c>
@@ -5245,7 +5239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A141" s="8">
         <v>44466</v>
       </c>
@@ -5267,7 +5261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A142" s="8">
         <v>44488</v>
       </c>
@@ -5289,7 +5283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A143" s="8">
         <v>44496</v>
       </c>
@@ -5311,7 +5305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A144" s="8">
         <v>44587</v>
       </c>
@@ -5333,7 +5327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A145" s="8">
         <v>44607</v>
       </c>
@@ -5355,7 +5349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A146" s="8">
         <v>44616</v>
       </c>
@@ -5377,7 +5371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A147" s="8">
         <v>44648</v>
       </c>
@@ -5399,7 +5393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A148" s="8">
         <v>44657</v>
       </c>
@@ -5421,7 +5415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A149" s="8">
         <v>44684</v>
       </c>
@@ -5443,7 +5437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A150" s="8">
         <v>44719</v>
       </c>
@@ -5465,7 +5459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A151" s="8">
         <v>44761</v>
       </c>
@@ -5487,7 +5481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A152" s="8">
         <v>44777</v>
       </c>
@@ -5509,7 +5503,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A153" s="8">
         <v>44817</v>
       </c>
@@ -5531,7 +5525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A154" s="8">
         <v>44845</v>
       </c>
@@ -5553,7 +5547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A155" s="8">
         <v>44858</v>
       </c>
@@ -5575,7 +5569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A156" s="8">
         <v>44874</v>
       </c>
@@ -5597,7 +5591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A157" s="8">
         <v>44908</v>
       </c>
@@ -5619,7 +5613,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A158" s="8">
         <v>44950</v>
       </c>
@@ -5641,7 +5635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A159" s="8">
         <v>44964</v>
       </c>
@@ -5663,7 +5657,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A160" s="8">
         <v>44998</v>
       </c>
@@ -5685,7 +5679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A161" s="8">
         <v>45042</v>
       </c>
@@ -5707,7 +5701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A162" s="8">
         <v>45068</v>
       </c>
@@ -5729,7 +5723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A163" s="8">
         <v>45084</v>
       </c>
@@ -5751,7 +5745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A164" s="8">
         <v>45126</v>
       </c>
@@ -5773,7 +5767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A165" s="8">
         <v>45139</v>
       </c>
@@ -5795,7 +5789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A166" s="8">
         <v>45183</v>
       </c>
@@ -5817,7 +5811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A167" s="8">
         <v>45203</v>
       </c>
@@ -5839,7 +5833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A168" s="8">
         <v>45224</v>
       </c>
@@ -5861,7 +5855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A169" s="8">
         <v>45243</v>
       </c>
@@ -5883,7 +5877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A170" s="8">
         <v>45274</v>
       </c>
@@ -5905,7 +5899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A171" s="8">
         <v>45293</v>
       </c>
@@ -5927,7 +5921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A172" s="8">
         <v>45336</v>
       </c>
@@ -5949,7 +5943,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A173" s="8">
         <v>45362</v>
       </c>
@@ -5971,7 +5965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A174" s="8">
         <v>45386</v>
       </c>
@@ -5993,7 +5987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A175" s="8">
         <v>45418</v>
       </c>
@@ -6015,7 +6009,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A176" s="8">
         <v>45454</v>
       </c>
@@ -6037,7 +6031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A177" s="8">
         <v>45475</v>
       </c>
@@ -6059,7 +6053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A178" s="8">
         <v>45516</v>
       </c>
@@ -6081,7 +6075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A179" s="8">
         <v>45544</v>
       </c>
@@ -6103,7 +6097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A180" s="8">
         <v>45587</v>
       </c>
@@ -6125,7 +6119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A181" s="8">
         <v>45588</v>
       </c>
@@ -6147,7 +6141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A182" s="8">
         <v>45607</v>
       </c>
@@ -6169,7 +6163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A183" s="8">
         <v>45630</v>
       </c>
@@ -6202,23 +6196,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB7B18C2-698C-4477-975F-BE3691B75A4A}">
-  <dimension ref="A1:L157"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O157"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="8" customWidth="1"/>
-    <col min="2" max="6" width="11.140625" style="6" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="6"/>
-    <col min="10" max="12" width="12.42578125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" style="8" customWidth="1"/>
+    <col min="2" max="6" width="11.1328125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.1328125" style="6"/>
+    <col min="8" max="8" width="15.3984375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="9.1328125" style="6"/>
+    <col min="10" max="12" width="12.3984375" style="6" customWidth="1"/>
     <col min="13" max="13" width="37" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="6"/>
+    <col min="14" max="16384" width="9.1328125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -6250,7 +6246,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="8">
         <v>40772</v>
       </c>
@@ -6266,28 +6262,29 @@
         <v>4.7449321283632502</v>
       </c>
       <c r="E3" s="6">
-        <v>117.497526620241</v>
+        <v>116.29244318898699</v>
       </c>
       <c r="F3" s="6">
         <v>1</v>
       </c>
+      <c r="H3" s="1"/>
       <c r="I3" s="9">
         <v>1</v>
       </c>
       <c r="J3" s="10" cm="1">
         <f t="array" ref="J3">INDEX(LINEST(_xlfn._xlws.FILTER($D$3:$D$1000,$F$3:$F$1000=$I3),CHOOSE({1,2},_xlfn._xlws.FILTER($E$3:$E$1000,$F$3:$F$1000=$I3),_xlfn._xlws.FILTER($B$3:$B$1000,$F$3:$F$1000=$I3)),TRUE,TRUE),1,1)</f>
-        <v>-6.376771180789017E-4</v>
+        <v>-6.3306230975986673E-4</v>
       </c>
       <c r="K3" s="11" cm="1">
         <f t="array" ref="K3">INDEX(LINEST(_xlfn._xlws.FILTER($D$3:$D$1000,$F$3:$F$1000=$I3),CHOOSE({1,2},_xlfn._xlws.FILTER($E$3:$E$1000,$F$3:$F$1000=$I3),_xlfn._xlws.FILTER($B$3:$B$1000,$F$3:$F$1000=$I3)),TRUE,TRUE),1,2)</f>
-        <v>-4.2371653363516872E-3</v>
+        <v>1.5839806211994992E-2</v>
       </c>
       <c r="L3" s="6" cm="1">
         <f t="array" ref="L3">INDEX(LINEST(_xlfn._xlws.FILTER($D$3:$D$1000,$F$3:$F$1000=$I3),CHOOSE({1,2},_xlfn._xlws.FILTER($E$3:$E$1000,$F$3:$F$1000=$I3),_xlfn._xlws.FILTER($B$3:$B$1000,$F$3:$F$1000=$I3)),TRUE,TRUE),1,3)</f>
-        <v>15.49733984826492</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>13.093339407601173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="8">
         <v>40954</v>
       </c>
@@ -6303,28 +6300,29 @@
         <v>5.1357984370502621</v>
       </c>
       <c r="E4" s="6">
-        <v>118.631361334617</v>
+        <v>115.15305553184901</v>
       </c>
       <c r="F4" s="6">
         <v>1</v>
       </c>
+      <c r="H4" s="1"/>
       <c r="I4" s="9">
         <v>2</v>
       </c>
       <c r="J4" s="10" cm="1">
         <f t="array" ref="J4">INDEX(LINEST(_xlfn._xlws.FILTER($D$3:$D$1000,$F$3:$F$1000=$I4),CHOOSE({1,2},_xlfn._xlws.FILTER($E$3:$E$1000,$F$3:$F$1000=$I4),_xlfn._xlws.FILTER($B$3:$B$1000,$F$3:$F$1000=$I4)),TRUE,TRUE),1,1)</f>
-        <v>9.2498302187147457E-7</v>
+        <v>-4.4069025339372386E-5</v>
       </c>
       <c r="K4" s="11" cm="1">
         <f t="array" ref="K4">INDEX(LINEST(_xlfn._xlws.FILTER($D$3:$D$1000,$F$3:$F$1000=$I4),CHOOSE({1,2},_xlfn._xlws.FILTER($E$3:$E$1000,$F$3:$F$1000=$I4),_xlfn._xlws.FILTER($B$3:$B$1000,$F$3:$F$1000=$I4)),TRUE,TRUE),1,2)</f>
-        <v>2.1528422204791953E-2</v>
+        <v>-7.2384427804628185E-2</v>
       </c>
       <c r="L4" s="6" cm="1">
         <f t="array" ref="L4">INDEX(LINEST(_xlfn._xlws.FILTER($D$3:$D$1000,$F$3:$F$1000=$I4),CHOOSE({1,2},_xlfn._xlws.FILTER($E$3:$E$1000,$F$3:$F$1000=$I4),_xlfn._xlws.FILTER($B$3:$B$1000,$F$3:$F$1000=$I4)),TRUE,TRUE),1,3)</f>
-        <v>0.49299611556827794</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>12.209021633002406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="8">
         <v>41052</v>
       </c>
@@ -6340,13 +6338,14 @@
         <v>5.0875963352323836</v>
       </c>
       <c r="E5" s="6">
-        <v>117.897650696554</v>
+        <v>117.064633694911</v>
       </c>
       <c r="F5" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" s="8">
         <v>41120</v>
       </c>
@@ -6362,13 +6361,14 @@
         <v>5.1873858058407549</v>
       </c>
       <c r="E6" s="6">
-        <v>117.209700945272</v>
+        <v>116.988970379736</v>
       </c>
       <c r="F6" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" s="8">
         <v>41201</v>
       </c>
@@ -6384,13 +6384,14 @@
         <v>4.9836066217083363</v>
       </c>
       <c r="E7" s="6">
-        <v>117.68303205827</v>
+        <v>113.971457666378</v>
       </c>
       <c r="F7" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
         <v>41309</v>
       </c>
@@ -6406,15 +6407,14 @@
         <v>4.8598124043616719</v>
       </c>
       <c r="E8" s="6">
-        <v>117.316991844622</v>
+        <v>114.732684942831</v>
       </c>
       <c r="F8" s="6">
         <v>1</v>
       </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="11"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" s="8">
         <v>41381</v>
       </c>
@@ -6430,15 +6430,17 @@
         <v>4.8903491282217537</v>
       </c>
       <c r="E9" s="6">
-        <v>116.912852971726</v>
+        <v>116.804673892279</v>
       </c>
       <c r="F9" s="6">
         <v>1</v>
       </c>
+      <c r="H9" s="1"/>
       <c r="J9" s="10"/>
-      <c r="K9" s="11"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" s="8">
         <v>41530</v>
       </c>
@@ -6454,13 +6456,17 @@
         <v>4.7405748229942946</v>
       </c>
       <c r="E10" s="6">
-        <v>115.707609754429</v>
+        <v>114.81513447854999</v>
       </c>
       <c r="F10" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H10" s="1"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" s="8">
         <v>41572</v>
       </c>
@@ -6476,13 +6482,14 @@
         <v>4.7535901911063645</v>
       </c>
       <c r="E11" s="6">
-        <v>117.12317003726599</v>
+        <v>114.590960210402</v>
       </c>
       <c r="F11" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" s="8">
         <v>41691</v>
       </c>
@@ -6498,13 +6505,16 @@
         <v>4.8040210447332568</v>
       </c>
       <c r="E12" s="6">
-        <v>116.877507651711</v>
+        <v>114.384884000033</v>
       </c>
       <c r="F12" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H12" s="1"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="8">
         <v>41807</v>
       </c>
@@ -6520,13 +6530,16 @@
         <v>4.8675344504555822</v>
       </c>
       <c r="E13" s="6">
-        <v>118.431038575868</v>
+        <v>116.111397062839</v>
       </c>
       <c r="F13" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H13" s="1"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" s="8">
         <v>41859</v>
       </c>
@@ -6542,13 +6555,14 @@
         <v>4.5951198501345898</v>
       </c>
       <c r="E14" s="6">
-        <v>118.13460728695701</v>
+        <v>115.67522113241</v>
       </c>
       <c r="F14" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" s="8">
         <v>41943</v>
       </c>
@@ -6564,13 +6578,14 @@
         <v>4.7095302013123339</v>
       </c>
       <c r="E15" s="6">
-        <v>117.582123829238</v>
+        <v>114.902802848273</v>
       </c>
       <c r="F15" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" s="8">
         <v>42046</v>
       </c>
@@ -6586,13 +6601,14 @@
         <v>4.677490847567717</v>
       </c>
       <c r="E16" s="6">
-        <v>118.64945403909</v>
+        <v>115.82091998282201</v>
       </c>
       <c r="F16" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="8">
         <v>42128</v>
       </c>
@@ -6608,13 +6624,14 @@
         <v>4.7184988712950942</v>
       </c>
       <c r="E17" s="6">
-        <v>117.487416488687</v>
+        <v>115.797268780729</v>
       </c>
       <c r="F17" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="8">
         <v>42219</v>
       </c>
@@ -6630,13 +6647,14 @@
         <v>4.3040650932041702</v>
       </c>
       <c r="E18" s="6">
-        <v>118.285709163981</v>
+        <v>114.956590743148</v>
       </c>
       <c r="F18" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="8">
         <v>42243</v>
       </c>
@@ -6652,13 +6670,14 @@
         <v>4.2268337452681797</v>
       </c>
       <c r="E19" s="6">
-        <v>117.330136457599</v>
+        <v>115.55116166203</v>
       </c>
       <c r="F19" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" s="8">
         <v>42255</v>
       </c>
@@ -6674,13 +6693,14 @@
         <v>4.3174881135363101</v>
       </c>
       <c r="E20" s="6">
-        <v>118.21042559736</v>
+        <v>114.495336725675</v>
       </c>
       <c r="F20" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="8">
         <v>42282</v>
       </c>
@@ -6696,13 +6716,14 @@
         <v>4.3694478524670215</v>
       </c>
       <c r="E21" s="6">
-        <v>120.567922650036</v>
+        <v>114.436575815279</v>
       </c>
       <c r="F21" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="8">
         <v>42310</v>
       </c>
@@ -6718,13 +6739,14 @@
         <v>4.219507705176107</v>
       </c>
       <c r="E22" s="6">
-        <v>119.760134633729</v>
+        <v>113.995681699884</v>
       </c>
       <c r="F22" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="8">
         <v>42319</v>
       </c>
@@ -6740,13 +6762,14 @@
         <v>4.3174881135363101</v>
       </c>
       <c r="E23" s="6">
-        <v>116.891661435397</v>
+        <v>114.821388977664</v>
       </c>
       <c r="F23" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="8">
         <v>42339</v>
       </c>
@@ -6762,13 +6785,14 @@
         <v>3.8066624897703196</v>
       </c>
       <c r="E24" s="6">
-        <v>118.66412001539101</v>
+        <v>115.157649464557</v>
       </c>
       <c r="F24" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="8">
         <v>42373</v>
       </c>
@@ -6784,13 +6808,14 @@
         <v>4.3307333402863311</v>
       </c>
       <c r="E25" s="6">
-        <v>118.244437348779</v>
+        <v>115.541923857496</v>
       </c>
       <c r="F25" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="8">
         <v>42401</v>
       </c>
@@ -6806,13 +6831,14 @@
         <v>4.3820266346738812</v>
       </c>
       <c r="E26" s="6">
-        <v>117.234120919874</v>
+        <v>115.080155039811</v>
       </c>
       <c r="F26" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="8">
         <v>42424</v>
       </c>
@@ -6828,13 +6854,14 @@
         <v>4.4067192472642533</v>
       </c>
       <c r="E27" s="6">
-        <v>117.31424643344501</v>
+        <v>115.753321572248</v>
       </c>
       <c r="F27" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="8">
         <v>42430</v>
       </c>
@@ -6850,13 +6877,14 @@
         <v>4.5217885770490405</v>
       </c>
       <c r="E28" s="6">
-        <v>117.778489756366</v>
+        <v>115.73130211642599</v>
       </c>
       <c r="F28" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="8">
         <v>42465</v>
       </c>
@@ -6872,13 +6900,14 @@
         <v>4.6051701859880918</v>
       </c>
       <c r="E29" s="6">
-        <v>116.785691507699</v>
+        <v>115.63538662000499</v>
       </c>
       <c r="F29" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="8">
         <v>42481</v>
       </c>
@@ -6894,13 +6923,14 @@
         <v>4.5432947822700038</v>
       </c>
       <c r="E30" s="6">
-        <v>117.480226611674</v>
+        <v>116.510686830407</v>
       </c>
       <c r="F30" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="8">
         <v>42485</v>
       </c>
@@ -6916,13 +6946,14 @@
         <v>4.290459441148391</v>
       </c>
       <c r="E31" s="6">
-        <v>117.86942878225901</v>
+        <v>116.730519764897</v>
       </c>
       <c r="F31" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="8">
         <v>42492</v>
       </c>
@@ -6938,13 +6969,14 @@
         <v>4.2484952420493594</v>
       </c>
       <c r="E32" s="6">
-        <v>118.439489626143</v>
+        <v>116.173193046924</v>
       </c>
       <c r="F32" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="8">
         <v>42499</v>
       </c>
@@ -6960,13 +6992,14 @@
         <v>4.290459441148391</v>
       </c>
       <c r="E33" s="6">
-        <v>118.231458884864</v>
+        <v>116.066587188166</v>
       </c>
       <c r="F33" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="8">
         <v>42501</v>
       </c>
@@ -6982,13 +7015,14 @@
         <v>4.2121275978784842</v>
       </c>
       <c r="E34" s="6">
-        <v>119.68094532159201</v>
+        <v>116.55817521101901</v>
       </c>
       <c r="F34" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="8">
         <v>42506</v>
       </c>
@@ -7004,13 +7038,14 @@
         <v>4.2484952420493594</v>
       </c>
       <c r="E35" s="6">
-        <v>119.567392996793</v>
+        <v>116.089740123656</v>
       </c>
       <c r="F35" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="8">
         <v>42527</v>
       </c>
@@ -7026,13 +7061,14 @@
         <v>4.2766661190160553</v>
       </c>
       <c r="E36" s="6">
-        <v>118.677069937947</v>
+        <v>116.066103082147</v>
       </c>
       <c r="F36" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="8">
         <v>42534</v>
       </c>
@@ -7048,13 +7084,14 @@
         <v>4.2341065045972597</v>
       </c>
       <c r="E37" s="6">
-        <v>117.542185410334</v>
+        <v>115.749620590335</v>
       </c>
       <c r="F37" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="8">
         <v>42548</v>
       </c>
@@ -7070,13 +7107,14 @@
         <v>4.2626798770413155</v>
       </c>
       <c r="E38" s="6">
-        <v>115.80910195887</v>
+        <v>116.059871125049</v>
       </c>
       <c r="F38" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" s="8">
         <v>42551</v>
       </c>
@@ -7092,13 +7130,14 @@
         <v>4.1820501426412067</v>
       </c>
       <c r="E39" s="6">
-        <v>116.45855449068399</v>
+        <v>115.705831519185</v>
       </c>
       <c r="F39" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="8">
         <v>42562</v>
       </c>
@@ -7114,13 +7153,14 @@
         <v>4.2046926193909657</v>
       </c>
       <c r="E40" s="6">
-        <v>116.272677863456</v>
+        <v>114.544957675067</v>
       </c>
       <c r="F40" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="8">
         <v>42570</v>
       </c>
@@ -7136,13 +7176,14 @@
         <v>4.2046926193909657</v>
       </c>
       <c r="E41" s="6">
-        <v>117.135490101214</v>
+        <v>115.632524081355</v>
       </c>
       <c r="F41" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="8">
         <v>42576</v>
       </c>
@@ -7158,13 +7199,14 @@
         <v>4.1588830833596715</v>
       </c>
       <c r="E42" s="6">
-        <v>117.89408653747</v>
+        <v>115.160819153831</v>
       </c>
       <c r="F42" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" s="8">
         <v>42583</v>
       </c>
@@ -7180,13 +7222,14 @@
         <v>4.1743872698956368</v>
       </c>
       <c r="E43" s="6">
-        <v>116.630986225201</v>
+        <v>115.539328577538</v>
       </c>
       <c r="F43" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="8">
         <v>42586</v>
       </c>
@@ -7202,13 +7245,14 @@
         <v>4.1588830833596715</v>
       </c>
       <c r="E44" s="6">
-        <v>116.402896336696</v>
+        <v>115.51319609225</v>
       </c>
       <c r="F44" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="8">
         <v>42591</v>
       </c>
@@ -7224,13 +7268,14 @@
         <v>4.2766661190160553</v>
       </c>
       <c r="E45" s="6">
-        <v>116.83053137429999</v>
+        <v>115.16336127506</v>
       </c>
       <c r="F45" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" s="8">
         <v>42597</v>
       </c>
@@ -7246,13 +7291,14 @@
         <v>4.0073331852324712</v>
       </c>
       <c r="E46" s="6">
-        <v>117.775349528175</v>
+        <v>114.79685485028899</v>
       </c>
       <c r="F46" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" s="8">
         <v>42604</v>
       </c>
@@ -7268,13 +7314,14 @@
         <v>4.1743872698956368</v>
       </c>
       <c r="E47" s="6">
-        <v>118.66491265469</v>
+        <v>114.530281196885</v>
       </c>
       <c r="F47" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A48" s="8">
         <v>42613</v>
       </c>
@@ -7290,13 +7337,14 @@
         <v>4.1743872698956368</v>
       </c>
       <c r="E48" s="6">
-        <v>118.166196677527</v>
+        <v>114.49055583153999</v>
       </c>
       <c r="F48" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A49" s="8">
         <v>42619</v>
       </c>
@@ -7312,13 +7360,14 @@
         <v>4.2341065045972597</v>
       </c>
       <c r="E49" s="6">
-        <v>118.95995865563999</v>
+        <v>114.483958625668</v>
       </c>
       <c r="F49" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A50" s="8">
         <v>42626</v>
       </c>
@@ -7334,13 +7383,14 @@
         <v>4.0430512678345503</v>
       </c>
       <c r="E50" s="6">
-        <v>117.447231582534</v>
+        <v>114.16856521655799</v>
       </c>
       <c r="F50" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="8">
         <v>42632</v>
       </c>
@@ -7356,13 +7406,14 @@
         <v>4.0775374439057197</v>
       </c>
       <c r="E51" s="6">
-        <v>117.53659176830701</v>
+        <v>114.59201226580601</v>
       </c>
       <c r="F51" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="8">
         <v>42641</v>
       </c>
@@ -7378,13 +7429,14 @@
         <v>4.1108738641733114</v>
       </c>
       <c r="E52" s="6">
-        <v>116.65276731856</v>
+        <v>114.28789151062099</v>
       </c>
       <c r="F52" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="8">
         <v>42646</v>
       </c>
@@ -7400,13 +7452,14 @@
         <v>4.1108738641733114</v>
       </c>
       <c r="E53" s="6">
-        <v>116.478438753433</v>
+        <v>114.506438280563</v>
       </c>
       <c r="F53" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="8">
         <v>42675</v>
       </c>
@@ -7422,13 +7475,14 @@
         <v>4.2341065045972597</v>
       </c>
       <c r="E54" s="6">
-        <v>116.87084649800001</v>
+        <v>115.350041304342</v>
       </c>
       <c r="F54" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" s="8">
         <v>42684</v>
       </c>
@@ -7444,13 +7498,14 @@
         <v>4.0474276424343492</v>
       </c>
       <c r="E55" s="6">
-        <v>116.667665071692</v>
+        <v>115.334693324372</v>
       </c>
       <c r="F55" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" s="8">
         <v>42711</v>
       </c>
@@ -7466,13 +7521,14 @@
         <v>4.1108738641733114</v>
       </c>
       <c r="E56" s="6">
-        <v>116.604976547109</v>
+        <v>115.697330050242</v>
       </c>
       <c r="F56" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" s="8">
         <v>42739</v>
       </c>
@@ -7488,13 +7544,14 @@
         <v>4.0430512678345503</v>
       </c>
       <c r="E57" s="6">
-        <v>116.656763823467</v>
+        <v>115.87773686126999</v>
       </c>
       <c r="F57" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" s="8">
         <v>42767</v>
       </c>
@@ -7510,13 +7567,14 @@
         <v>3.912023005428146</v>
       </c>
       <c r="E58" s="6">
-        <v>116.343129150183</v>
+        <v>115.28805305705301</v>
       </c>
       <c r="F58" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" s="8">
         <v>42768</v>
       </c>
@@ -7532,13 +7590,14 @@
         <v>3.9608131695975781</v>
       </c>
       <c r="E59" s="6">
-        <v>116.85765647138599</v>
+        <v>115.41541579277801</v>
       </c>
       <c r="F59" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" s="8">
         <v>42795</v>
       </c>
@@ -7554,13 +7613,14 @@
         <v>3.912023005428146</v>
       </c>
       <c r="E60" s="6">
-        <v>117.121547462311</v>
+        <v>115.362542218965</v>
       </c>
       <c r="F60" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="8">
         <v>42829</v>
       </c>
@@ -7576,13 +7636,14 @@
         <v>3.8918202981106265</v>
       </c>
       <c r="E61" s="6">
-        <v>117.573647237841</v>
+        <v>117.299298342726</v>
       </c>
       <c r="F61" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" s="8">
         <v>42856</v>
       </c>
@@ -7598,13 +7659,14 @@
         <v>3.9512437185814275</v>
       </c>
       <c r="E62" s="6">
-        <v>118.61561564557201</v>
+        <v>116.886066752329</v>
       </c>
       <c r="F62" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A63" s="8">
         <v>42858</v>
       </c>
@@ -7620,13 +7682,14 @@
         <v>3.8781214537524642</v>
       </c>
       <c r="E63" s="6">
-        <v>118.121451318596</v>
+        <v>116.608825952526</v>
       </c>
       <c r="F63" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H63" s="1"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A64" s="8">
         <v>42893</v>
       </c>
@@ -7642,13 +7705,14 @@
         <v>3.8712010109078911</v>
       </c>
       <c r="E64" s="6">
-        <v>118.802180503207</v>
+        <v>117.725037650274</v>
       </c>
       <c r="F64" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A65" s="8">
         <v>42922</v>
       </c>
@@ -7664,13 +7728,14 @@
         <v>3.8501476017100584</v>
       </c>
       <c r="E65" s="6">
-        <v>117.718576434932</v>
+        <v>115.914734591133</v>
       </c>
       <c r="F65" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A66" s="8">
         <v>42948</v>
       </c>
@@ -7686,13 +7751,14 @@
         <v>3.9512437185814275</v>
       </c>
       <c r="E66" s="6">
-        <v>116.030077930966</v>
+        <v>115.51370472017</v>
       </c>
       <c r="F66" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" s="8">
         <v>42984</v>
       </c>
@@ -7708,13 +7774,14 @@
         <v>4.0430512678345503</v>
       </c>
       <c r="E67" s="6">
-        <v>116.143270719646</v>
+        <v>115.019705051256</v>
       </c>
       <c r="F67" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A68" s="8">
         <v>43006</v>
       </c>
@@ -7730,13 +7797,14 @@
         <v>3.8815637979434374</v>
       </c>
       <c r="E68" s="6">
-        <v>116.03824266572499</v>
+        <v>114.35077905857899</v>
       </c>
       <c r="F68" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A69" s="8">
         <v>43011</v>
       </c>
@@ -7752,13 +7820,14 @@
         <v>3.970291913552122</v>
       </c>
       <c r="E69" s="6">
-        <v>117.29937525768899</v>
+        <v>114.624974696709</v>
       </c>
       <c r="F69" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A70" s="8">
         <v>43073</v>
       </c>
@@ -7774,13 +7843,14 @@
         <v>3.2958368660043291</v>
       </c>
       <c r="E70" s="6">
-        <v>116.779068051699</v>
+        <v>114.67776041340301</v>
       </c>
       <c r="F70" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H70" s="1"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A71" s="8">
         <v>43080</v>
       </c>
@@ -7796,13 +7866,14 @@
         <v>3.8394523125933104</v>
       </c>
       <c r="E71" s="6">
-        <v>117.50152148276599</v>
+        <v>115.575727434491</v>
       </c>
       <c r="F71" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H71" s="1"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A72" s="8">
         <v>43103</v>
       </c>
@@ -7818,13 +7889,14 @@
         <v>3.8501476017100584</v>
       </c>
       <c r="E72" s="6">
-        <v>117.733618184691</v>
+        <v>115.614617021802</v>
       </c>
       <c r="F72" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H72" s="1"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A73" s="8">
         <v>43132</v>
       </c>
@@ -7840,13 +7912,14 @@
         <v>3.9318256327243257</v>
       </c>
       <c r="E73" s="6">
-        <v>117.75865386400601</v>
+        <v>115.82092894787</v>
       </c>
       <c r="F73" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H73" s="1"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A74" s="8">
         <v>43165</v>
       </c>
@@ -7862,13 +7935,14 @@
         <v>3.8066624897703196</v>
       </c>
       <c r="E74" s="6">
-        <v>117.39129023564099</v>
+        <v>115.769286565279</v>
       </c>
       <c r="F74" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H74" s="1"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="8">
         <v>43173</v>
       </c>
@@ -7884,13 +7958,14 @@
         <v>3.7612001156935624</v>
       </c>
       <c r="E75" s="6">
-        <v>116.13462683831401</v>
+        <v>115.35963688929399</v>
       </c>
       <c r="F75" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H75" s="1"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A76" s="8">
         <v>43194</v>
       </c>
@@ -7906,13 +7981,14 @@
         <v>3.7612001156935624</v>
       </c>
       <c r="E76" s="6">
-        <v>117.63302440900399</v>
+        <v>115.767986733776</v>
       </c>
       <c r="F76" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A77" s="8">
         <v>43227</v>
       </c>
@@ -7928,13 +8004,14 @@
         <v>3.7376696182833684</v>
       </c>
       <c r="E77" s="6">
-        <v>117.81194948007099</v>
+        <v>117.360964365103</v>
       </c>
       <c r="F77" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A78" s="8">
         <v>43257</v>
       </c>
@@ -7950,13 +8027,14 @@
         <v>3.5835189384561099</v>
       </c>
       <c r="E78" s="6">
-        <v>116.715473141774</v>
+        <v>117.28682808983601</v>
       </c>
       <c r="F78" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H78" s="1"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A79" s="8">
         <v>43291</v>
       </c>
@@ -7972,13 +8050,14 @@
         <v>3.6971782569286304</v>
       </c>
       <c r="E79" s="6">
-        <v>116.408024813723</v>
+        <v>115.737071466473</v>
       </c>
       <c r="F79" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H79" s="1"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A80" s="8">
         <v>43325</v>
       </c>
@@ -7994,13 +8073,14 @@
         <v>3.5553480614894135</v>
       </c>
       <c r="E80" s="6">
-        <v>116.926014508484</v>
+        <v>114.904799812375</v>
       </c>
       <c r="F80" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H80" s="1"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" s="8">
         <v>43348</v>
       </c>
@@ -8016,13 +8096,14 @@
         <v>3.8066624897703196</v>
       </c>
       <c r="E81" s="6">
-        <v>116.06441041553499</v>
+        <v>114.582789358276</v>
       </c>
       <c r="F81" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H81" s="1"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A82" s="8">
         <v>43363</v>
       </c>
@@ -8038,13 +8119,14 @@
         <v>3.6375861597263857</v>
       </c>
       <c r="E82" s="6">
-        <v>116.108224767518</v>
+        <v>113.822409218963</v>
       </c>
       <c r="F82" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A83" s="8">
         <v>43374</v>
       </c>
@@ -8060,13 +8142,14 @@
         <v>3.2580965380214821</v>
       </c>
       <c r="E83" s="6">
-        <v>117.058161708066</v>
+        <v>114.49498257382101</v>
       </c>
       <c r="F83" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H83" s="1"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" s="8">
         <v>43410</v>
       </c>
@@ -8082,13 +8165,14 @@
         <v>3.7612001156935624</v>
       </c>
       <c r="E84" s="6">
-        <v>117.23284149518901</v>
+        <v>114.671832089807</v>
       </c>
       <c r="F84" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H84" s="1"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85" s="8">
         <v>43445</v>
       </c>
@@ -8104,13 +8188,14 @@
         <v>3.536116699561525</v>
       </c>
       <c r="E85" s="6">
-        <v>117.427671122516</v>
+        <v>115.44706135835401</v>
       </c>
       <c r="F85" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H85" s="1"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86" s="8">
         <v>43446</v>
       </c>
@@ -8126,13 +8211,14 @@
         <v>3.8286413964890951</v>
       </c>
       <c r="E86" s="6">
-        <v>117.51776556588599</v>
+        <v>114.737554864109</v>
       </c>
       <c r="F86" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H86" s="1"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87" s="8">
         <v>43467</v>
       </c>
@@ -8148,13 +8234,14 @@
         <v>3.6375861597263857</v>
       </c>
       <c r="E87" s="6">
-        <v>116.94009292533499</v>
+        <v>114.931411883545</v>
       </c>
       <c r="F87" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H87" s="1"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88" s="8">
         <v>43657</v>
       </c>
@@ -8170,13 +8257,14 @@
         <v>3.2958368660043291</v>
       </c>
       <c r="E88" s="6">
-        <v>118.824358888753</v>
+        <v>114.90227568044</v>
       </c>
       <c r="F88" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H88" s="1"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89" s="8">
         <v>43703</v>
       </c>
@@ -8192,13 +8280,14 @@
         <v>3.4011973816621555</v>
       </c>
       <c r="E89" s="6">
-        <v>117.599752499773</v>
+        <v>114.466081486736</v>
       </c>
       <c r="F89" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H89" s="1"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A90" s="8">
         <v>43738</v>
       </c>
@@ -8214,13 +8303,14 @@
         <v>3.3672958299864741</v>
       </c>
       <c r="E90" s="6">
-        <v>117.069754253794</v>
+        <v>113.870581158164</v>
       </c>
       <c r="F90" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H90" s="1"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" s="8">
         <v>43748</v>
       </c>
@@ -8236,13 +8326,14 @@
         <v>3.3672958299864741</v>
       </c>
       <c r="E91" s="6">
-        <v>117.51869237282</v>
+        <v>114.057902244454</v>
       </c>
       <c r="F91" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H91" s="1"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92" s="8">
         <v>43774</v>
       </c>
@@ -8258,13 +8349,14 @@
         <v>3.3672958299864741</v>
       </c>
       <c r="E92" s="6">
-        <v>116.312992549104</v>
+        <v>114.936574930356</v>
       </c>
       <c r="F92" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H92" s="1"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93" s="8">
         <v>43803</v>
       </c>
@@ -8280,13 +8372,14 @@
         <v>3.3322045101752038</v>
       </c>
       <c r="E93" s="6">
-        <v>116.694145746782</v>
+        <v>115.300350986591</v>
       </c>
       <c r="F93" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H93" s="1"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94" s="8">
         <v>43809</v>
       </c>
@@ -8302,13 +8395,14 @@
         <v>3.3032169733019514</v>
       </c>
       <c r="E94" s="6">
-        <v>117.729900687285</v>
+        <v>115.18913092595101</v>
       </c>
       <c r="F94" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H94" s="1"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95" s="8">
         <v>43837</v>
       </c>
@@ -8324,13 +8418,14 @@
         <v>3.1780538303479458</v>
       </c>
       <c r="E95" s="6">
-        <v>116.784943290774</v>
+        <v>115.101656608501</v>
       </c>
       <c r="F95" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H95" s="1"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96" s="8">
         <v>43880</v>
       </c>
@@ -8346,13 +8441,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E96" s="6">
-        <v>116.727700372435</v>
+        <v>116.032581147325</v>
       </c>
       <c r="F96" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H96" s="1"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A97" s="8">
         <v>43902</v>
       </c>
@@ -8368,13 +8464,14 @@
         <v>3.202746442938317</v>
       </c>
       <c r="E97" s="6">
-        <v>116.092561353837</v>
+        <v>114.77558220259201</v>
       </c>
       <c r="F97" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H97" s="1"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" s="8">
         <v>44035</v>
       </c>
@@ -8390,13 +8487,14 @@
         <v>2.7725887222397811</v>
       </c>
       <c r="E98" s="6">
-        <v>117.213479577943</v>
+        <v>116.119392445806</v>
       </c>
       <c r="F98" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H98" s="1"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99" s="8">
         <v>44054</v>
       </c>
@@ -8412,13 +8510,14 @@
         <v>3.3672958299864741</v>
       </c>
       <c r="E99" s="6">
-        <v>117.640364127791</v>
+        <v>115.68201049011201</v>
       </c>
       <c r="F99" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H99" s="1"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100" s="8">
         <v>44083</v>
       </c>
@@ -8434,13 +8533,14 @@
         <v>3.2958368660043291</v>
       </c>
       <c r="E100" s="6">
-        <v>117.87382034122901</v>
+        <v>114.67440151858</v>
       </c>
       <c r="F100" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H100" s="1"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101" s="8">
         <v>44111</v>
       </c>
@@ -8456,13 +8556,14 @@
         <v>3.1311369105601941</v>
       </c>
       <c r="E101" s="6">
-        <v>117.614127922885</v>
+        <v>114.78443394060599</v>
       </c>
       <c r="F101" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H101" s="1"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102" s="8">
         <v>44116</v>
       </c>
@@ -8478,13 +8579,14 @@
         <v>3.4011973816621555</v>
       </c>
       <c r="E102" s="6">
-        <v>117.25547609975</v>
+        <v>114.036745260318</v>
       </c>
       <c r="F102" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H102" s="1"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103" s="8">
         <v>44147</v>
       </c>
@@ -8500,13 +8602,14 @@
         <v>2.8903717578961645</v>
       </c>
       <c r="E103" s="6">
-        <v>119.06995566916299</v>
+        <v>115.426136945016</v>
       </c>
       <c r="F103" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H103" s="1"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A104" s="8">
         <v>44175</v>
       </c>
@@ -8522,13 +8625,14 @@
         <v>2.9496883350525844</v>
       </c>
       <c r="E104" s="6">
-        <v>117.76226383772401</v>
+        <v>115.07975425157299</v>
       </c>
       <c r="F104" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H104" s="1"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" s="8">
         <v>44216</v>
       </c>
@@ -8544,13 +8648,14 @@
         <v>3.0910424533583161</v>
       </c>
       <c r="E105" s="6">
-        <v>118.52206073325399</v>
+        <v>115.565456400168</v>
       </c>
       <c r="F105" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H105" s="1"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106" s="8">
         <v>44236</v>
       </c>
@@ -8566,13 +8671,14 @@
         <v>2.5649493574615367</v>
       </c>
       <c r="E106" s="6">
-        <v>118.64345932898701</v>
+        <v>115.75829898967901</v>
       </c>
       <c r="F106" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H106" s="1"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107" s="8">
         <v>44265</v>
       </c>
@@ -8588,13 +8694,14 @@
         <v>3.1780538303479458</v>
       </c>
       <c r="E107" s="6">
-        <v>119.219325454958</v>
+        <v>114.493182573667</v>
       </c>
       <c r="F107" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H107" s="1"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108" s="8">
         <v>44277</v>
       </c>
@@ -8610,13 +8717,14 @@
         <v>3.0155349008501706</v>
       </c>
       <c r="E108" s="6">
-        <v>116.429487718495</v>
+        <v>114.387938623688</v>
       </c>
       <c r="F108" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H108" s="1"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109" s="8">
         <v>44299</v>
       </c>
@@ -8632,13 +8740,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E109" s="6">
-        <v>118.88340600735999</v>
+        <v>114.39135619711701</v>
       </c>
       <c r="F109" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H109" s="1"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110" s="8">
         <v>44333</v>
       </c>
@@ -8654,13 +8763,14 @@
         <v>3.0910424533583161</v>
       </c>
       <c r="E110" s="6">
-        <v>117.973751731148</v>
+        <v>115.558522671841</v>
       </c>
       <c r="F110" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H110" s="1"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A111" s="8">
         <v>44371</v>
       </c>
@@ -8676,13 +8786,14 @@
         <v>2.8903717578961645</v>
       </c>
       <c r="E111" s="6">
-        <v>117.375860919533</v>
+        <v>115.97278692831</v>
       </c>
       <c r="F111" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H111" s="1"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A112" s="8">
         <v>44375</v>
       </c>
@@ -8698,13 +8809,14 @@
         <v>3.0910424533583161</v>
       </c>
       <c r="E112" s="6">
-        <v>116.950862691989</v>
+        <v>116.307064930104</v>
       </c>
       <c r="F112" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H112" s="1"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" s="8">
         <v>44384</v>
       </c>
@@ -8720,13 +8832,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E113" s="6">
-        <v>116.78373623543899</v>
+        <v>115.820110896301</v>
       </c>
       <c r="F113" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H113" s="1"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" s="8">
         <v>44434</v>
       </c>
@@ -8742,13 +8855,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E114" s="6">
-        <v>117.028090406057</v>
+        <v>115.12387372503601</v>
       </c>
       <c r="F114" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H114" s="1"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" s="8">
         <v>44496</v>
       </c>
@@ -8764,13 +8878,14 @@
         <v>2.7911651078127169</v>
       </c>
       <c r="E115" s="6">
-        <v>117.55724952659099</v>
+        <v>114.04167325327499</v>
       </c>
       <c r="F115" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H115" s="1"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" s="8">
         <v>44502</v>
       </c>
@@ -8786,13 +8901,14 @@
         <v>3.0910424533583161</v>
       </c>
       <c r="E116" s="6">
-        <v>116.59290154422099</v>
+        <v>114.81017162777501</v>
       </c>
       <c r="F116" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H116" s="1"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117" s="8">
         <v>44607</v>
       </c>
@@ -8808,13 +8924,14 @@
         <v>2.6810215287142909</v>
       </c>
       <c r="E117" s="6">
-        <v>118.07010610942601</v>
+        <v>115.760824579626</v>
       </c>
       <c r="F117" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H117" s="1"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" s="8">
         <v>44614</v>
       </c>
@@ -8830,13 +8947,14 @@
         <v>3.2580965380214821</v>
       </c>
       <c r="E118" s="6">
-        <v>116.140692766879</v>
+        <v>115.71497669436</v>
       </c>
       <c r="F118" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H118" s="1"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" s="8">
         <v>44641</v>
       </c>
@@ -8852,13 +8970,14 @@
         <v>2.7080502011022101</v>
       </c>
       <c r="E119" s="6">
-        <v>116.750503531448</v>
+        <v>115.08356292861301</v>
       </c>
       <c r="F119" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H119" s="1"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A120" s="8">
         <v>44655</v>
       </c>
@@ -8874,13 +8993,14 @@
         <v>2.8213788864092133</v>
       </c>
       <c r="E120" s="6">
-        <v>117.345020468372</v>
+        <v>115.172354624863</v>
       </c>
       <c r="F120" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H120" s="1"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="8">
         <v>44658</v>
       </c>
@@ -8896,13 +9016,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E121" s="6">
-        <v>116.876234455537</v>
+        <v>115.446105899014</v>
       </c>
       <c r="F121" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H121" s="1"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122" s="8">
         <v>44699</v>
       </c>
@@ -8918,13 +9039,14 @@
         <v>2.8903717578961645</v>
       </c>
       <c r="E122" s="6">
-        <v>117.30908779809</v>
+        <v>115.88376423584501</v>
       </c>
       <c r="F122" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H122" s="1"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="8">
         <v>44734</v>
       </c>
@@ -8940,13 +9062,14 @@
         <v>2.8332133440562162</v>
       </c>
       <c r="E123" s="6">
-        <v>118.18392700342601</v>
+        <v>118.090322492574</v>
       </c>
       <c r="F123" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H123" s="1"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124" s="8">
         <v>44769</v>
       </c>
@@ -8962,13 +9085,14 @@
         <v>3.044522437723423</v>
       </c>
       <c r="E124" s="6">
-        <v>117.20630814138801</v>
+        <v>116.185232382461</v>
       </c>
       <c r="F124" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H124" s="1"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125" s="8">
         <v>44782</v>
       </c>
@@ -8984,13 +9108,14 @@
         <v>2.8903717578961645</v>
       </c>
       <c r="E125" s="6">
-        <v>117.556523817423</v>
+        <v>115.919823300524</v>
       </c>
       <c r="F125" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H125" s="1"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" s="8">
         <v>44825</v>
       </c>
@@ -9006,13 +9131,14 @@
         <v>3.2188758248682006</v>
       </c>
       <c r="E126" s="6">
-        <v>120.58907370438</v>
+        <v>114.354273716943</v>
       </c>
       <c r="F126" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H126" s="1"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A127" s="8">
         <v>44846</v>
       </c>
@@ -9028,13 +9154,14 @@
         <v>3.3877743613300146</v>
       </c>
       <c r="E127" s="6">
-        <v>117.246095645145</v>
+        <v>113.87912955524</v>
       </c>
       <c r="F127" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H127" s="1"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A128" s="8">
         <v>44851</v>
       </c>
@@ -9050,13 +9177,14 @@
         <v>2.9444389791664403</v>
       </c>
       <c r="E128" s="6">
-        <v>117.901437973181</v>
+        <v>113.940693215876</v>
       </c>
       <c r="F128" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H128" s="1"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" s="8">
         <v>44881</v>
       </c>
@@ -9072,13 +9200,14 @@
         <v>3.1780538303479458</v>
       </c>
       <c r="E129" s="6">
-        <v>117.20830482322501</v>
+        <v>115.229719296535</v>
       </c>
       <c r="F129" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H129" s="1"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130" s="8">
         <v>44901</v>
       </c>
@@ -9094,13 +9223,14 @@
         <v>3.3322045101752038</v>
       </c>
       <c r="E130" s="6">
-        <v>117.574850911007</v>
+        <v>114.977349000655</v>
       </c>
       <c r="F130" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H130" s="1"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" s="8">
         <v>44935</v>
       </c>
@@ -9116,13 +9246,14 @@
         <v>3.4965075614664802</v>
       </c>
       <c r="E131" s="6">
-        <v>116.85191038564901</v>
+        <v>114.527131600441</v>
       </c>
       <c r="F131" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H131" s="1"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132" s="8">
         <v>44964</v>
       </c>
@@ -9138,13 +9269,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E132" s="6">
-        <v>116.485274698003</v>
+        <v>114.789928382376</v>
       </c>
       <c r="F132" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H132" s="1"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133" s="8">
         <v>44991</v>
       </c>
@@ -9160,13 +9292,14 @@
         <v>2.8903717578961645</v>
       </c>
       <c r="E133" s="6">
-        <v>117.29781901593699</v>
+        <v>114.306324887773</v>
       </c>
       <c r="F133" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H133" s="1"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134" s="8">
         <v>45020</v>
       </c>
@@ -9182,13 +9315,14 @@
         <v>3.3322045101752038</v>
       </c>
       <c r="E134" s="6">
-        <v>116.656349710795</v>
+        <v>114.22826191073101</v>
       </c>
       <c r="F134" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H134" s="1"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A135" s="8">
         <v>45028</v>
       </c>
@@ -9204,13 +9338,14 @@
         <v>2.8903717578961645</v>
       </c>
       <c r="E135" s="6">
-        <v>116.986379546525</v>
+        <v>114.21629767339699</v>
       </c>
       <c r="F135" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H135" s="1"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" s="8">
         <v>45063</v>
       </c>
@@ -9226,13 +9361,14 @@
         <v>3.0910424533583161</v>
       </c>
       <c r="E136" s="6">
-        <v>117.2778304065</v>
+        <v>117.637866433076</v>
       </c>
       <c r="F136" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H136" s="1"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" s="8">
         <v>45084</v>
       </c>
@@ -9248,13 +9384,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E137" s="6">
-        <v>116.986308867509</v>
+        <v>115.604019858462</v>
       </c>
       <c r="F137" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H137" s="1"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" s="8">
         <v>45118</v>
       </c>
@@ -9270,13 +9407,14 @@
         <v>2.9444389791664403</v>
       </c>
       <c r="E138" s="6">
-        <v>116.476411090312</v>
+        <v>114.928749214571</v>
       </c>
       <c r="F138" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H138" s="1"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="8">
         <v>45140</v>
       </c>
@@ -9292,13 +9430,14 @@
         <v>3.044522437723423</v>
       </c>
       <c r="E139" s="6">
-        <v>118.235229264014</v>
+        <v>115.261245140873</v>
       </c>
       <c r="F139" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H139" s="1"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" s="8">
         <v>45182</v>
       </c>
@@ -9314,13 +9453,14 @@
         <v>3.2188758248682006</v>
       </c>
       <c r="E140" s="6">
-        <v>116.46775387953799</v>
+        <v>114.066933511364</v>
       </c>
       <c r="F140" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H140" s="1"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" s="8">
         <v>45223</v>
       </c>
@@ -9336,13 +9476,14 @@
         <v>2.7788192719904172</v>
       </c>
       <c r="E141" s="6">
-        <v>116.219847575511</v>
+        <v>113.954363874031</v>
       </c>
       <c r="F141" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H141" s="1"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A142" s="8">
         <v>45231</v>
       </c>
@@ -9358,13 +9499,14 @@
         <v>3.2580965380214821</v>
       </c>
       <c r="E142" s="6">
-        <v>117.94518930686</v>
+        <v>114.579440260778</v>
       </c>
       <c r="F142" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H142" s="1"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A143" s="8">
         <v>45280</v>
       </c>
@@ -9380,13 +9522,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E143" s="6">
-        <v>116.356397189121</v>
+        <v>114.90347535076</v>
       </c>
       <c r="F143" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H143" s="1"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" s="8">
         <v>45295</v>
       </c>
@@ -9402,13 +9545,14 @@
         <v>3.0910424533583161</v>
       </c>
       <c r="E144" s="6">
-        <v>117.07027105605199</v>
+        <v>114.703900753566</v>
       </c>
       <c r="F144" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H144" s="1"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" s="8">
         <v>45334</v>
       </c>
@@ -9424,13 +9568,14 @@
         <v>2.8903717578961645</v>
       </c>
       <c r="E145" s="6">
-        <v>116.814875948718</v>
+        <v>114.259039914079</v>
       </c>
       <c r="F145" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H145" s="1"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A146" s="8">
         <v>45357</v>
       </c>
@@ -9446,13 +9591,14 @@
         <v>2.6390573296152584</v>
       </c>
       <c r="E146" s="6">
-        <v>116.17423669490699</v>
+        <v>114.53061545096</v>
       </c>
       <c r="F146" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H146" s="1"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" s="8">
         <v>45385</v>
       </c>
@@ -9468,13 +9614,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E147" s="6">
-        <v>116.264638581111</v>
+        <v>114.419556096374</v>
       </c>
       <c r="F147" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H147" s="1"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A148" s="8">
         <v>45392</v>
       </c>
@@ -9490,13 +9637,14 @@
         <v>2.8154087194227095</v>
       </c>
       <c r="E148" s="6">
-        <v>116.44589802126001</v>
+        <v>114.588326279635</v>
       </c>
       <c r="F148" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H148" s="1"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A149" s="8">
         <v>45418</v>
       </c>
@@ -9512,13 +9660,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E149" s="6">
-        <v>115.717652178067</v>
+        <v>114.558935708696</v>
       </c>
       <c r="F149" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H149" s="1"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A150" s="8">
         <v>45460</v>
       </c>
@@ -9534,13 +9683,14 @@
         <v>2.8332133440562162</v>
       </c>
       <c r="E150" s="6">
-        <v>116.501340008791</v>
+        <v>115.808472842101</v>
       </c>
       <c r="F150" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H150" s="1"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A151" s="8">
         <v>45481</v>
       </c>
@@ -9556,13 +9706,14 @@
         <v>3.044522437723423</v>
       </c>
       <c r="E151" s="6">
-        <v>116.403402156971</v>
+        <v>115.713968229773</v>
       </c>
       <c r="F151" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H151" s="1"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A152" s="8">
         <v>45518</v>
       </c>
@@ -9578,13 +9729,14 @@
         <v>2.6390573296152584</v>
       </c>
       <c r="E152" s="6">
-        <v>116.83734586362201</v>
+        <v>115.05389153809099</v>
       </c>
       <c r="F152" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H152" s="1"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" s="8">
         <v>45551</v>
       </c>
@@ -9600,13 +9752,14 @@
         <v>2.9957322735539909</v>
       </c>
       <c r="E153" s="6">
-        <v>116.40285304502601</v>
+        <v>113.83493605205</v>
       </c>
       <c r="F153" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H153" s="1"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A154" s="8">
         <v>45574</v>
       </c>
@@ -9622,13 +9775,14 @@
         <v>3.784189633918261</v>
       </c>
       <c r="E154" s="6">
-        <v>116.82720008525</v>
+        <v>113.93659386979</v>
       </c>
       <c r="F154" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H154" s="1"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A155" s="8">
         <v>45580</v>
       </c>
@@ -9644,13 +9798,14 @@
         <v>2.760009940032921</v>
       </c>
       <c r="E155" s="6">
-        <v>116.01834948123999</v>
+        <v>114.246271846428</v>
       </c>
       <c r="F155" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H155" s="1"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A156" s="8">
         <v>45600</v>
       </c>
@@ -9666,13 +9821,14 @@
         <v>3.6375861597263857</v>
       </c>
       <c r="E156" s="6">
-        <v>117.941284734386</v>
+        <v>114.69814748026999</v>
       </c>
       <c r="F156" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H156" s="1"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A157" s="8">
         <v>45629</v>
       </c>
@@ -9688,11 +9844,12 @@
         <v>2.9444389791664403</v>
       </c>
       <c r="E157" s="6">
-        <v>117.034318915791</v>
+        <v>115.07192099425799</v>
       </c>
       <c r="F157" s="6">
         <v>2</v>
       </c>
+      <c r="H157" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F157">
@@ -9706,9 +9863,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A4A7C42-E6C4-4111-B079-D39941D85DB3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -9721,9 +9878,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E31C90-10A0-404B-8ACE-7D837146D995}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.1328125" style="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
